--- a/Tools/Luban/DataTables/Datas/H_合成.xlsx
+++ b/Tools/Luban/DataTables/Datas/H_合成.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABDC34A-3D40-4B6C-9FA5-37E7E92E0C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7DDD7A-D66D-483C-8F06-AC1FEF6F6709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6870" yWindow="3740" windowWidth="30180" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17430" yWindow="6160" windowWidth="18780" windowHeight="12970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -765,7 +765,7 @@
         <v>2013</v>
       </c>
       <c r="F5" s="9">
-        <v>5003</v>
+        <v>5009</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>

--- a/Tools/Luban/DataTables/Datas/H_合成.xlsx
+++ b/Tools/Luban/DataTables/Datas/H_合成.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7DDD7A-D66D-483C-8F06-AC1FEF6F6709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B608903-BD72-4978-8A09-C05CE4F09366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17430" yWindow="6160" windowWidth="18780" windowHeight="12970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$148</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -69,10 +72,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>土豆-巨大作物</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>工程内音效名称</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -119,12 +118,161 @@
     <t>costMainBuckets_2</t>
   </si>
   <si>
-    <t>花椰菜汤</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>合成音效</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆-房子</t>
+  </si>
+  <si>
+    <t>蘑菇-房子</t>
+  </si>
+  <si>
+    <t>南瓜-房子</t>
+  </si>
+  <si>
+    <t>胡萝卜-房子</t>
+  </si>
+  <si>
+    <t>水甜菜-房子</t>
+  </si>
+  <si>
+    <t>番茄-红-房子</t>
+  </si>
+  <si>
+    <t>番茄-橙-房子</t>
+  </si>
+  <si>
+    <t>番茄-黄-房子</t>
+  </si>
+  <si>
+    <t>番茄-绿-房子</t>
+  </si>
+  <si>
+    <t>番茄-青-房子</t>
+  </si>
+  <si>
+    <t>番茄-蓝-房子</t>
+  </si>
+  <si>
+    <t>番茄-紫-房子</t>
+  </si>
+  <si>
+    <t>花椰菜-房子</t>
+  </si>
+  <si>
+    <t>猕猴桃-房子</t>
+  </si>
+  <si>
+    <t>野草-房子</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;蘑菇味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;南瓜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;胡萝卜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;南瓜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;胡萝卜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;胡萝卜味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-红番茄&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-红番茄&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-红番茄&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-花椰菜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-花椰菜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-猕猴桃&amp;野草味</t>
   </si>
 </sst>
 </file>
@@ -661,16 +809,16 @@
         <v>5</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="F1" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -684,13 +832,13 @@
         <v>3</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>3</v>
@@ -704,19 +852,19 @@
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -730,16 +878,16 @@
         <v>9</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>19</v>
-      </c>
       <c r="G4" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
@@ -759,14 +907,15 @@
         <v>24</v>
       </c>
       <c r="D5" s="9">
-        <v>5001</v>
+        <v>3001</v>
       </c>
       <c r="E5" s="9">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="F5" s="9">
-        <v>5009</v>
-      </c>
+        <v>6001</v>
+      </c>
+      <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="L5" s="9"/>
@@ -779,17 +928,18 @@
         <v>1002</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D6" s="11">
-        <v>2001</v>
-      </c>
-      <c r="E6" s="11">
-        <v>2001</v>
+        <v>3002</v>
+      </c>
+      <c r="E6" s="9">
+        <v>2016</v>
       </c>
       <c r="F6" s="11">
-        <v>3001</v>
-      </c>
+        <v>6002</v>
+      </c>
+      <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="L6" s="9"/>
@@ -798,11 +948,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="B7" s="9">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="9">
+        <v>3003</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F7" s="9">
+        <v>6003</v>
+      </c>
+      <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="L7" s="9"/>
@@ -811,11 +972,21 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="B8" s="9">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="9">
+        <v>3004</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F8" s="9">
+        <v>6004</v>
+      </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="L8" s="9"/>
@@ -825,11 +996,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+      <c r="B9" s="9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="9">
+        <v>3005</v>
+      </c>
+      <c r="E9" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F9" s="9">
+        <v>6005</v>
+      </c>
+      <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
       <c r="L9" s="9"/>
@@ -839,11 +1021,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="B10" s="9">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="9">
+        <v>3006</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F10" s="9">
+        <v>6006</v>
+      </c>
+      <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
       <c r="L10" s="9"/>
@@ -853,11 +1046,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="B11" s="9">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="9">
+        <v>3007</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F11" s="9">
+        <v>6007</v>
+      </c>
+      <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="L11" s="9"/>
@@ -867,11 +1071,21 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="B12" s="9">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="9">
+        <v>3008</v>
+      </c>
+      <c r="E12" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F12" s="9">
+        <v>6008</v>
+      </c>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
       <c r="L12" s="9"/>
@@ -881,11 +1095,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="B13" s="9">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="9">
+        <v>3009</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F13" s="9">
+        <v>6009</v>
+      </c>
+      <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="L13" s="9"/>
@@ -895,11 +1120,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="B14" s="9">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="9">
+        <v>3010</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F14" s="9">
+        <v>6010</v>
+      </c>
+      <c r="H14" s="9"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
       <c r="L14" s="9"/>
@@ -909,11 +1145,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="B15" s="9">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="9">
+        <v>3011</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F15" s="9">
+        <v>6011</v>
+      </c>
+      <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="L15" s="9"/>
@@ -923,11 +1170,21 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="B16" s="9">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="9">
+        <v>3012</v>
+      </c>
+      <c r="E16" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F16" s="9">
+        <v>6012</v>
+      </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
       <c r="L16" s="9"/>
@@ -937,11 +1194,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="B17" s="9">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="9">
+        <v>3013</v>
+      </c>
+      <c r="E17" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F17" s="9">
+        <v>6013</v>
+      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="L17" s="9"/>
@@ -951,11 +1219,21 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="B18" s="9">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="9">
+        <v>3014</v>
+      </c>
+      <c r="E18" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F18" s="9">
+        <v>6014</v>
+      </c>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
@@ -968,11 +1246,21 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="B19" s="9">
+        <v>1015</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="9">
+        <v>3015</v>
+      </c>
+      <c r="E19" s="9">
+        <v>2016</v>
+      </c>
+      <c r="F19" s="9">
+        <v>6015</v>
+      </c>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -983,30 +1271,50 @@
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+    <row r="20" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11">
+        <v>2001</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="11">
+        <v>2001</v>
+      </c>
+      <c r="E20" s="10">
+        <v>2002</v>
+      </c>
+      <c r="F20" s="11">
+        <v>5009</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
+      <c r="B21" s="9">
+        <v>2002</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="9">
+        <v>2001</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2003</v>
+      </c>
+      <c r="F21" s="9">
+        <v>5010</v>
+      </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -1019,11 +1327,21 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
+      <c r="B22" s="9">
+        <v>2003</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="9">
+        <v>2001</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2004</v>
+      </c>
+      <c r="F22" s="9">
+        <v>5011</v>
+      </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
@@ -1036,11 +1354,21 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
+      <c r="B23" s="9">
+        <v>2004</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="9">
+        <v>2001</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2005</v>
+      </c>
+      <c r="F23" s="9">
+        <v>5012</v>
+      </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -1053,11 +1381,21 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
+      <c r="B24" s="9">
+        <v>2005</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="9">
+        <v>2001</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2006</v>
+      </c>
+      <c r="F24" s="9">
+        <v>5013</v>
+      </c>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
@@ -1070,11 +1408,21 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
+      <c r="B25" s="9">
+        <v>2006</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="9">
+        <v>2001</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2007</v>
+      </c>
+      <c r="F25" s="9">
+        <v>5014</v>
+      </c>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -1087,11 +1435,21 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
+      <c r="B26" s="9">
+        <v>2007</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="9">
+        <v>2001</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F26" s="9">
+        <v>5015</v>
+      </c>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -1104,11 +1462,21 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
+      <c r="B27" s="9">
+        <v>2008</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="9">
+        <v>2001</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F27" s="9">
+        <v>5016</v>
+      </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -1121,11 +1489,21 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
+      <c r="B28" s="9">
+        <v>2009</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="9">
+        <v>2002</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2003</v>
+      </c>
+      <c r="F28" s="9">
+        <v>5017</v>
+      </c>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -1138,11 +1516,21 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
+      <c r="B29" s="9">
+        <v>2010</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="9">
+        <v>2002</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2004</v>
+      </c>
+      <c r="F29" s="9">
+        <v>5018</v>
+      </c>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
@@ -1155,11 +1543,21 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
+      <c r="B30" s="9">
+        <v>2011</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="9">
+        <v>2002</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2005</v>
+      </c>
+      <c r="F30" s="9">
+        <v>5019</v>
+      </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -1172,11 +1570,21 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
+      <c r="B31" s="9">
+        <v>2012</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="9">
+        <v>2002</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2006</v>
+      </c>
+      <c r="F31" s="9">
+        <v>5020</v>
+      </c>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -1189,11 +1597,21 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
+      <c r="B32" s="9">
+        <v>2013</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="9">
+        <v>2002</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2007</v>
+      </c>
+      <c r="F32" s="9">
+        <v>5021</v>
+      </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
@@ -1206,11 +1624,21 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
+      <c r="B33" s="9">
+        <v>2014</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="9">
+        <v>2002</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F33" s="9">
+        <v>5022</v>
+      </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
@@ -1223,11 +1651,21 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
+      <c r="B34" s="9">
+        <v>2015</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="9">
+        <v>2002</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F34" s="9">
+        <v>5023</v>
+      </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
@@ -1240,11 +1678,21 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
+      <c r="B35" s="9">
+        <v>2016</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="9">
+        <v>2003</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2004</v>
+      </c>
+      <c r="F35" s="9">
+        <v>5024</v>
+      </c>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
@@ -1257,11 +1705,21 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
+      <c r="B36" s="9">
+        <v>2017</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="9">
+        <v>2003</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2005</v>
+      </c>
+      <c r="F36" s="9">
+        <v>5025</v>
+      </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
@@ -1274,11 +1732,21 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
+      <c r="B37" s="9">
+        <v>2018</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="9">
+        <v>2003</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2006</v>
+      </c>
+      <c r="F37" s="9">
+        <v>5026</v>
+      </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -1291,11 +1759,21 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
+      <c r="B38" s="9">
+        <v>2019</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="9">
+        <v>2003</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2007</v>
+      </c>
+      <c r="F38" s="9">
+        <v>5027</v>
+      </c>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -1308,11 +1786,21 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
+      <c r="B39" s="9">
+        <v>2020</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="9">
+        <v>2003</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F39" s="9">
+        <v>5028</v>
+      </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -1325,11 +1813,21 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
+      <c r="B40" s="9">
+        <v>2021</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="9">
+        <v>2003</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F40" s="9">
+        <v>5029</v>
+      </c>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
@@ -1342,11 +1840,21 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
+      <c r="B41" s="9">
+        <v>2022</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" s="9">
+        <v>2004</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2005</v>
+      </c>
+      <c r="F41" s="9">
+        <v>5030</v>
+      </c>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -1359,11 +1867,21 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
+      <c r="B42" s="9">
+        <v>2023</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="9">
+        <v>2004</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2006</v>
+      </c>
+      <c r="F42" s="9">
+        <v>5031</v>
+      </c>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -1376,11 +1894,21 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
+      <c r="B43" s="9">
+        <v>2024</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="9">
+        <v>2004</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2007</v>
+      </c>
+      <c r="F43" s="9">
+        <v>5032</v>
+      </c>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -1393,11 +1921,21 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
+      <c r="B44" s="9">
+        <v>2025</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="9">
+        <v>2004</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F44" s="9">
+        <v>5033</v>
+      </c>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -1410,11 +1948,21 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
+      <c r="B45" s="9">
+        <v>2026</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D45" s="9">
+        <v>2004</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F45" s="9">
+        <v>5034</v>
+      </c>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -1427,11 +1975,21 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
+      <c r="B46" s="9">
+        <v>2027</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="9">
+        <v>2005</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2006</v>
+      </c>
+      <c r="F46" s="9">
+        <v>5035</v>
+      </c>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
@@ -1444,11 +2002,21 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
+      <c r="B47" s="9">
+        <v>2028</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" s="9">
+        <v>2005</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2007</v>
+      </c>
+      <c r="F47" s="9">
+        <v>5036</v>
+      </c>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -1461,11 +2029,21 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
+      <c r="B48" s="9">
+        <v>2029</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" s="9">
+        <v>2005</v>
+      </c>
+      <c r="E48" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F48" s="9">
+        <v>5037</v>
+      </c>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
@@ -1478,11 +2056,21 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
+      <c r="B49" s="9">
+        <v>2030</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="9">
+        <v>2005</v>
+      </c>
+      <c r="E49" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F49" s="9">
+        <v>5038</v>
+      </c>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
@@ -1495,13 +2083,23 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
+      <c r="B50" s="9">
+        <v>2031</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" s="9">
+        <v>2006</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2007</v>
+      </c>
+      <c r="F50" s="9">
+        <v>5039</v>
+      </c>
       <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
+      <c r="H50" s="11"/>
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
@@ -1512,13 +2110,23 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
+      <c r="B51" s="9">
+        <v>2032</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="9">
+        <v>2006</v>
+      </c>
+      <c r="E51" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F51" s="9">
+        <v>5040</v>
+      </c>
       <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
+      <c r="H51" s="12"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
@@ -1529,13 +2137,23 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
+      <c r="B52" s="9">
+        <v>2033</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D52" s="9">
+        <v>2006</v>
+      </c>
+      <c r="E52" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F52" s="9">
+        <v>5041</v>
+      </c>
       <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
+      <c r="H52" s="3"/>
       <c r="I52" s="9"/>
       <c r="J52" s="9"/>
       <c r="K52" s="9"/>
@@ -1546,13 +2164,23 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
+      <c r="B53" s="9">
+        <v>2034</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" s="9">
+        <v>2007</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F53" s="9">
+        <v>5042</v>
+      </c>
       <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
+      <c r="H53" s="3"/>
       <c r="I53" s="9"/>
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
@@ -1563,13 +2191,23 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
+      <c r="B54" s="9">
+        <v>2035</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="9">
+        <v>2007</v>
+      </c>
+      <c r="E54" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F54" s="9">
+        <v>5043</v>
+      </c>
       <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
+      <c r="H54" s="3"/>
       <c r="I54" s="9"/>
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
@@ -1580,13 +2218,23 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
+      <c r="B55" s="9">
+        <v>2036</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" s="9">
+        <v>2008</v>
+      </c>
+      <c r="E55" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F55" s="9">
+        <v>5044</v>
+      </c>
       <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
+      <c r="H55" s="3"/>
       <c r="I55" s="9"/>
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
@@ -1600,10 +2248,9 @@
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
+      <c r="H56" s="3"/>
       <c r="I56" s="9"/>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
@@ -1617,10 +2264,9 @@
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
+      <c r="H57" s="3"/>
       <c r="I57" s="9"/>
       <c r="J57" s="9"/>
       <c r="K57" s="9"/>
@@ -1634,10 +2280,9 @@
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
+      <c r="H58" s="3"/>
       <c r="I58" s="9"/>
       <c r="J58" s="9"/>
       <c r="K58" s="9"/>
@@ -1651,10 +2296,9 @@
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
+      <c r="H59" s="3"/>
       <c r="I59" s="9"/>
       <c r="J59" s="9"/>
       <c r="K59" s="9"/>
@@ -1668,10 +2312,9 @@
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
+      <c r="H60" s="3"/>
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
@@ -1685,10 +2328,9 @@
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
+      <c r="H61" s="3"/>
       <c r="I61" s="9"/>
       <c r="J61" s="9"/>
       <c r="K61" s="9"/>
@@ -1702,10 +2344,9 @@
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
+      <c r="H62" s="3"/>
       <c r="I62" s="9"/>
       <c r="J62" s="9"/>
       <c r="K62" s="9"/>
@@ -1719,10 +2360,9 @@
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
+      <c r="H63" s="3"/>
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
       <c r="K63" s="9"/>
@@ -1736,10 +2376,9 @@
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
+      <c r="H64" s="3"/>
       <c r="I64" s="9"/>
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>
@@ -1753,10 +2392,9 @@
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
       <c r="F65" s="11"/>
       <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
+      <c r="H65" s="3"/>
       <c r="I65" s="11"/>
       <c r="J65" s="11"/>
       <c r="K65" s="11"/>
@@ -1770,10 +2408,9 @@
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
       <c r="F66" s="12"/>
       <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
+      <c r="H66" s="3"/>
       <c r="I66" s="12"/>
       <c r="J66" s="12"/>
       <c r="K66" s="12"/>
@@ -1787,7 +2424,6 @@
       <c r="B67" s="3"/>
       <c r="C67" s="7"/>
       <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
@@ -1804,7 +2440,6 @@
       <c r="B68" s="3"/>
       <c r="C68" s="7"/>
       <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
@@ -1821,7 +2456,6 @@
       <c r="B69" s="3"/>
       <c r="C69" s="7"/>
       <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
@@ -1838,7 +2472,6 @@
       <c r="B70" s="3"/>
       <c r="C70" s="7"/>
       <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
@@ -1855,7 +2488,6 @@
       <c r="B71" s="3"/>
       <c r="C71" s="7"/>
       <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
@@ -1872,7 +2504,6 @@
       <c r="B72" s="3"/>
       <c r="C72" s="7"/>
       <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
@@ -1889,7 +2520,6 @@
       <c r="B73" s="3"/>
       <c r="C73" s="7"/>
       <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
@@ -1906,7 +2536,6 @@
       <c r="B74" s="3"/>
       <c r="C74" s="7"/>
       <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
@@ -1923,7 +2552,6 @@
       <c r="B75" s="3"/>
       <c r="C75" s="7"/>
       <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
@@ -1940,7 +2568,6 @@
       <c r="B76" s="3"/>
       <c r="C76" s="7"/>
       <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
@@ -1957,7 +2584,6 @@
       <c r="B77" s="3"/>
       <c r="C77" s="7"/>
       <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
@@ -1974,7 +2600,6 @@
       <c r="B78" s="3"/>
       <c r="C78" s="7"/>
       <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
@@ -1991,7 +2616,6 @@
       <c r="B79" s="3"/>
       <c r="C79" s="7"/>
       <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
@@ -2008,7 +2632,6 @@
       <c r="B80" s="3"/>
       <c r="C80" s="7"/>
       <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
@@ -2025,7 +2648,6 @@
       <c r="B81" s="3"/>
       <c r="C81" s="7"/>
       <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
@@ -2042,7 +2664,6 @@
       <c r="B82" s="3"/>
       <c r="C82" s="7"/>
       <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
@@ -2059,7 +2680,6 @@
       <c r="B83" s="3"/>
       <c r="C83" s="7"/>
       <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
@@ -2076,7 +2696,6 @@
       <c r="B84" s="3"/>
       <c r="C84" s="7"/>
       <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
@@ -2093,7 +2712,6 @@
       <c r="B85" s="3"/>
       <c r="C85" s="7"/>
       <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
@@ -2110,7 +2728,6 @@
       <c r="B86" s="3"/>
       <c r="C86" s="7"/>
       <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
@@ -2127,7 +2744,6 @@
       <c r="B87" s="3"/>
       <c r="C87" s="7"/>
       <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
@@ -2144,7 +2760,6 @@
       <c r="B88" s="3"/>
       <c r="C88" s="7"/>
       <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
@@ -2161,7 +2776,6 @@
       <c r="B89" s="3"/>
       <c r="C89" s="7"/>
       <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
@@ -2178,7 +2792,6 @@
       <c r="B90" s="3"/>
       <c r="C90" s="7"/>
       <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
@@ -2195,7 +2808,6 @@
       <c r="B91" s="3"/>
       <c r="C91" s="7"/>
       <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
@@ -2212,7 +2824,6 @@
       <c r="B92" s="3"/>
       <c r="C92" s="7"/>
       <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
@@ -2229,7 +2840,6 @@
       <c r="B93" s="3"/>
       <c r="C93" s="7"/>
       <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
@@ -2246,7 +2856,6 @@
       <c r="B94" s="3"/>
       <c r="C94" s="7"/>
       <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
@@ -2263,7 +2872,6 @@
       <c r="B95" s="3"/>
       <c r="C95" s="7"/>
       <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
@@ -2280,7 +2888,6 @@
       <c r="B96" s="3"/>
       <c r="C96" s="7"/>
       <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
@@ -2297,7 +2904,6 @@
       <c r="B97" s="3"/>
       <c r="C97" s="7"/>
       <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
@@ -2314,7 +2920,6 @@
       <c r="B98" s="3"/>
       <c r="C98" s="7"/>
       <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
@@ -2331,7 +2936,6 @@
       <c r="B99" s="3"/>
       <c r="C99" s="7"/>
       <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
@@ -2348,7 +2952,6 @@
       <c r="B100" s="3"/>
       <c r="C100" s="7"/>
       <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
@@ -2365,7 +2968,6 @@
       <c r="B101" s="3"/>
       <c r="C101" s="7"/>
       <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
@@ -2382,7 +2984,6 @@
       <c r="B102" s="3"/>
       <c r="C102" s="7"/>
       <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
@@ -2399,7 +3000,6 @@
       <c r="B103" s="3"/>
       <c r="C103" s="7"/>
       <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -2416,7 +3016,6 @@
       <c r="B104" s="3"/>
       <c r="C104" s="7"/>
       <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -2433,7 +3032,6 @@
       <c r="B105" s="3"/>
       <c r="C105" s="7"/>
       <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -2450,7 +3048,6 @@
       <c r="B106" s="3"/>
       <c r="C106" s="7"/>
       <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -2467,7 +3064,6 @@
       <c r="B107" s="3"/>
       <c r="C107" s="7"/>
       <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -2484,7 +3080,6 @@
       <c r="B108" s="3"/>
       <c r="C108" s="7"/>
       <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -2501,7 +3096,6 @@
       <c r="B109" s="3"/>
       <c r="C109" s="7"/>
       <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
@@ -2518,7 +3112,6 @@
       <c r="B110" s="3"/>
       <c r="C110" s="7"/>
       <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
@@ -2535,7 +3128,6 @@
       <c r="B111" s="3"/>
       <c r="C111" s="7"/>
       <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
@@ -2552,7 +3144,6 @@
       <c r="B112" s="3"/>
       <c r="C112" s="7"/>
       <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
@@ -2569,7 +3160,6 @@
       <c r="B113" s="3"/>
       <c r="C113" s="7"/>
       <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
@@ -2586,7 +3176,6 @@
       <c r="B114" s="3"/>
       <c r="C114" s="7"/>
       <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
       <c r="H114" s="3"/>
@@ -2603,7 +3192,6 @@
       <c r="B115" s="3"/>
       <c r="C115" s="7"/>
       <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
@@ -2620,7 +3208,6 @@
       <c r="B116" s="3"/>
       <c r="C116" s="7"/>
       <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
@@ -2637,7 +3224,6 @@
       <c r="B117" s="3"/>
       <c r="C117" s="7"/>
       <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
@@ -2654,7 +3240,6 @@
       <c r="B118" s="3"/>
       <c r="C118" s="7"/>
       <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
@@ -2671,7 +3256,6 @@
       <c r="B119" s="3"/>
       <c r="C119" s="7"/>
       <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
@@ -2688,7 +3272,6 @@
       <c r="B120" s="3"/>
       <c r="C120" s="7"/>
       <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
@@ -2705,7 +3288,6 @@
       <c r="B121" s="3"/>
       <c r="C121" s="7"/>
       <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
       <c r="H121" s="3"/>
@@ -2722,7 +3304,6 @@
       <c r="B122" s="3"/>
       <c r="C122" s="7"/>
       <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
@@ -2739,7 +3320,6 @@
       <c r="B123" s="3"/>
       <c r="C123" s="7"/>
       <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
       <c r="H123" s="3"/>
@@ -2756,7 +3336,6 @@
       <c r="B124" s="3"/>
       <c r="C124" s="7"/>
       <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
       <c r="H124" s="3"/>
@@ -2773,7 +3352,6 @@
       <c r="B125" s="3"/>
       <c r="C125" s="7"/>
       <c r="D125" s="3"/>
-      <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
@@ -2790,7 +3368,6 @@
       <c r="B126" s="3"/>
       <c r="C126" s="7"/>
       <c r="D126" s="3"/>
-      <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
@@ -2807,7 +3384,6 @@
       <c r="B127" s="3"/>
       <c r="C127" s="7"/>
       <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
       <c r="H127" s="3"/>
@@ -2824,7 +3400,6 @@
       <c r="B128" s="3"/>
       <c r="C128" s="7"/>
       <c r="D128" s="3"/>
-      <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3"/>
       <c r="H128" s="3"/>
@@ -2841,7 +3416,6 @@
       <c r="B129" s="3"/>
       <c r="C129" s="7"/>
       <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
       <c r="H129" s="3"/>
@@ -2858,7 +3432,6 @@
       <c r="B130" s="3"/>
       <c r="C130" s="7"/>
       <c r="D130" s="3"/>
-      <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
       <c r="H130" s="3"/>
@@ -2875,7 +3448,6 @@
       <c r="B131" s="3"/>
       <c r="C131" s="7"/>
       <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
       <c r="H131" s="3"/>
@@ -2892,7 +3464,6 @@
       <c r="B132" s="3"/>
       <c r="C132" s="7"/>
       <c r="D132" s="3"/>
-      <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
@@ -2909,7 +3480,6 @@
       <c r="B133" s="3"/>
       <c r="C133" s="7"/>
       <c r="D133" s="3"/>
-      <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3"/>
       <c r="H133" s="3"/>
@@ -2926,7 +3496,6 @@
       <c r="B134" s="3"/>
       <c r="C134" s="7"/>
       <c r="D134" s="3"/>
-      <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
       <c r="H134" s="3"/>
@@ -2943,7 +3512,6 @@
       <c r="B135" s="3"/>
       <c r="C135" s="7"/>
       <c r="D135" s="3"/>
-      <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
       <c r="H135" s="3"/>
@@ -2960,7 +3528,6 @@
       <c r="B136" s="3"/>
       <c r="C136" s="7"/>
       <c r="D136" s="3"/>
-      <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3"/>
       <c r="H136" s="3"/>
@@ -2977,7 +3544,6 @@
       <c r="B137" s="3"/>
       <c r="C137" s="7"/>
       <c r="D137" s="3"/>
-      <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3"/>
       <c r="H137" s="3"/>
@@ -2994,7 +3560,6 @@
       <c r="B138" s="3"/>
       <c r="C138" s="7"/>
       <c r="D138" s="3"/>
-      <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3"/>
       <c r="H138" s="3"/>
@@ -3011,7 +3576,6 @@
       <c r="B139" s="3"/>
       <c r="C139" s="7"/>
       <c r="D139" s="3"/>
-      <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
       <c r="H139" s="3"/>
@@ -3028,7 +3592,6 @@
       <c r="B140" s="3"/>
       <c r="C140" s="7"/>
       <c r="D140" s="3"/>
-      <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
       <c r="H140" s="3"/>
@@ -3045,7 +3608,6 @@
       <c r="B141" s="3"/>
       <c r="C141" s="7"/>
       <c r="D141" s="3"/>
-      <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3"/>
       <c r="H141" s="3"/>
@@ -3062,7 +3624,6 @@
       <c r="B142" s="3"/>
       <c r="C142" s="7"/>
       <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3"/>
       <c r="H142" s="3"/>
@@ -3079,7 +3640,6 @@
       <c r="B143" s="3"/>
       <c r="C143" s="7"/>
       <c r="D143" s="3"/>
-      <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
       <c r="H143" s="3"/>
@@ -3096,7 +3656,6 @@
       <c r="B144" s="3"/>
       <c r="C144" s="7"/>
       <c r="D144" s="3"/>
-      <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
       <c r="H144" s="3"/>
@@ -3113,7 +3672,6 @@
       <c r="B145" s="3"/>
       <c r="C145" s="7"/>
       <c r="D145" s="3"/>
-      <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3"/>
       <c r="H145" s="3"/>
@@ -3130,7 +3688,6 @@
       <c r="B146" s="3"/>
       <c r="C146" s="7"/>
       <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3"/>
       <c r="H146" s="3"/>
@@ -3147,7 +3704,6 @@
       <c r="B147" s="3"/>
       <c r="C147" s="7"/>
       <c r="D147" s="3"/>
-      <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
       <c r="H147" s="3"/>
@@ -3164,7 +3720,6 @@
       <c r="B148" s="3"/>
       <c r="C148" s="7"/>
       <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3"/>
       <c r="H148" s="3"/>
@@ -3181,7 +3736,6 @@
       <c r="B149" s="3"/>
       <c r="C149" s="7"/>
       <c r="D149" s="3"/>
-      <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3"/>
       <c r="H149" s="3"/>
@@ -3198,7 +3752,6 @@
       <c r="B150" s="3"/>
       <c r="C150" s="7"/>
       <c r="D150" s="3"/>
-      <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3"/>
       <c r="H150" s="3"/>
@@ -3215,7 +3768,6 @@
       <c r="B151" s="3"/>
       <c r="C151" s="7"/>
       <c r="D151" s="3"/>
-      <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3"/>
       <c r="H151" s="3"/>
@@ -3232,7 +3784,6 @@
       <c r="B152" s="3"/>
       <c r="C152" s="7"/>
       <c r="D152" s="3"/>
-      <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
       <c r="H152" s="3"/>
@@ -3249,7 +3800,6 @@
       <c r="B153" s="3"/>
       <c r="C153" s="7"/>
       <c r="D153" s="3"/>
-      <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
       <c r="H153" s="3"/>
@@ -3266,7 +3816,6 @@
       <c r="B154" s="3"/>
       <c r="C154" s="7"/>
       <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
       <c r="H154" s="3"/>
@@ -3283,7 +3832,6 @@
       <c r="B155" s="3"/>
       <c r="C155" s="7"/>
       <c r="D155" s="3"/>
-      <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
       <c r="H155" s="3"/>
@@ -3300,7 +3848,6 @@
       <c r="B156" s="3"/>
       <c r="C156" s="7"/>
       <c r="D156" s="3"/>
-      <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
       <c r="H156" s="3"/>
@@ -3317,7 +3864,6 @@
       <c r="B157" s="3"/>
       <c r="C157" s="7"/>
       <c r="D157" s="3"/>
-      <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
       <c r="H157" s="3"/>
@@ -3334,7 +3880,6 @@
       <c r="B158" s="3"/>
       <c r="C158" s="7"/>
       <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
       <c r="H158" s="3"/>
@@ -3351,7 +3896,6 @@
       <c r="B159" s="3"/>
       <c r="C159" s="7"/>
       <c r="D159" s="3"/>
-      <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
       <c r="H159" s="3"/>
@@ -3368,7 +3912,6 @@
       <c r="B160" s="3"/>
       <c r="C160" s="7"/>
       <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
       <c r="H160" s="3"/>
@@ -3385,7 +3928,6 @@
       <c r="B161" s="3"/>
       <c r="C161" s="7"/>
       <c r="D161" s="3"/>
-      <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
       <c r="H161" s="3"/>
@@ -3402,7 +3944,6 @@
       <c r="B162" s="3"/>
       <c r="C162" s="7"/>
       <c r="D162" s="3"/>
-      <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
       <c r="H162" s="3"/>
@@ -3419,7 +3960,6 @@
       <c r="B163" s="3"/>
       <c r="C163" s="7"/>
       <c r="D163" s="3"/>
-      <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
       <c r="H163" s="3"/>
@@ -3916,6 +4456,7 @@
       <c r="L192" s="8"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:O148" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tools/Luban/DataTables/Datas/H_合成.xlsx
+++ b/Tools/Luban/DataTables/Datas/H_合成.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18360"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -270,7 +270,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,13 +298,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -461,7 +454,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,6 +476,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -887,137 +886,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1040,22 +1039,25 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1378,7 +1380,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P192"/>
-  <sheetFormatPr defaultColWidth="12.1666666666667" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="12.1666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="12.1666666666667" style="3"/>
     <col min="3" max="3" width="22.8333333333333" style="3" customWidth="1"/>
@@ -1392,7 +1394,7 @@
     <col min="15" max="16384" width="12.1666666666667" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:16">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1418,7 +1420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:16">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
@@ -1444,7 +1446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:16">
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
@@ -1516,8 +1518,8 @@
       <c r="E5" s="8">
         <v>3001</v>
       </c>
-      <c r="F5" s="8">
-        <v>2016</v>
+      <c r="F5" s="10">
+        <v>5045</v>
       </c>
       <c r="G5" s="8">
         <v>6001</v>
@@ -1534,19 +1536,19 @@
       <c r="B6" s="8">
         <v>1002</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="8">
         <v>1</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="11">
         <v>3002</v>
       </c>
-      <c r="F6" s="8">
-        <v>2016</v>
-      </c>
-      <c r="G6" s="10">
+      <c r="F6" s="10">
+        <v>5045</v>
+      </c>
+      <c r="G6" s="11">
         <v>6002</v>
       </c>
       <c r="I6" s="8"/>
@@ -1570,8 +1572,8 @@
       <c r="E7" s="8">
         <v>3003</v>
       </c>
-      <c r="F7" s="8">
-        <v>2016</v>
+      <c r="F7" s="10">
+        <v>5045</v>
       </c>
       <c r="G7" s="8">
         <v>6003</v>
@@ -1597,8 +1599,8 @@
       <c r="E8" s="8">
         <v>3004</v>
       </c>
-      <c r="F8" s="8">
-        <v>2016</v>
+      <c r="F8" s="10">
+        <v>5045</v>
       </c>
       <c r="G8" s="8">
         <v>6004</v>
@@ -1624,8 +1626,8 @@
       <c r="E9" s="8">
         <v>3005</v>
       </c>
-      <c r="F9" s="8">
-        <v>2016</v>
+      <c r="F9" s="10">
+        <v>5045</v>
       </c>
       <c r="G9" s="8">
         <v>6005</v>
@@ -1652,8 +1654,8 @@
       <c r="E10" s="8">
         <v>3006</v>
       </c>
-      <c r="F10" s="8">
-        <v>2016</v>
+      <c r="F10" s="10">
+        <v>5045</v>
       </c>
       <c r="G10" s="8">
         <v>6006</v>
@@ -1680,8 +1682,8 @@
       <c r="E11" s="8">
         <v>3007</v>
       </c>
-      <c r="F11" s="8">
-        <v>2016</v>
+      <c r="F11" s="10">
+        <v>5045</v>
       </c>
       <c r="G11" s="8">
         <v>6007</v>
@@ -1708,8 +1710,8 @@
       <c r="E12" s="8">
         <v>3008</v>
       </c>
-      <c r="F12" s="8">
-        <v>2016</v>
+      <c r="F12" s="10">
+        <v>5045</v>
       </c>
       <c r="G12" s="8">
         <v>6008</v>
@@ -1735,8 +1737,8 @@
       <c r="E13" s="8">
         <v>3009</v>
       </c>
-      <c r="F13" s="8">
-        <v>2016</v>
+      <c r="F13" s="10">
+        <v>5045</v>
       </c>
       <c r="G13" s="8">
         <v>6009</v>
@@ -1763,8 +1765,8 @@
       <c r="E14" s="8">
         <v>3010</v>
       </c>
-      <c r="F14" s="8">
-        <v>2016</v>
+      <c r="F14" s="10">
+        <v>5045</v>
       </c>
       <c r="G14" s="8">
         <v>6010</v>
@@ -1791,8 +1793,8 @@
       <c r="E15" s="8">
         <v>3011</v>
       </c>
-      <c r="F15" s="8">
-        <v>2016</v>
+      <c r="F15" s="10">
+        <v>5045</v>
       </c>
       <c r="G15" s="8">
         <v>6011</v>
@@ -1819,8 +1821,8 @@
       <c r="E16" s="8">
         <v>3012</v>
       </c>
-      <c r="F16" s="8">
-        <v>2016</v>
+      <c r="F16" s="10">
+        <v>5045</v>
       </c>
       <c r="G16" s="8">
         <v>6012</v>
@@ -1846,8 +1848,8 @@
       <c r="E17" s="8">
         <v>3013</v>
       </c>
-      <c r="F17" s="8">
-        <v>2016</v>
+      <c r="F17" s="10">
+        <v>5045</v>
       </c>
       <c r="G17" s="8">
         <v>6013</v>
@@ -1874,8 +1876,8 @@
       <c r="E18" s="8">
         <v>3014</v>
       </c>
-      <c r="F18" s="8">
-        <v>2016</v>
+      <c r="F18" s="10">
+        <v>5045</v>
       </c>
       <c r="G18" s="8">
         <v>6014</v>
@@ -1904,8 +1906,8 @@
       <c r="E19" s="8">
         <v>3015</v>
       </c>
-      <c r="F19" s="8">
-        <v>2016</v>
+      <c r="F19" s="10">
+        <v>5045</v>
       </c>
       <c r="G19" s="8">
         <v>6015</v>
@@ -1921,34 +1923,34 @@
       <c r="P19" s="8"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:16">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11">
         <v>2001</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="11">
         <v>2</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="11">
         <v>2001</v>
       </c>
       <c r="F20" s="1">
         <v>2002</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="11">
         <v>5009</v>
       </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="8"/>
@@ -2841,7 +2843,7 @@
         <v>5039</v>
       </c>
       <c r="H50" s="8"/>
-      <c r="I50" s="10"/>
+      <c r="I50" s="11"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
@@ -2871,7 +2873,7 @@
         <v>5040</v>
       </c>
       <c r="H51" s="8"/>
-      <c r="I51" s="11"/>
+      <c r="I51" s="12"/>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
@@ -3154,43 +3156,43 @@
       <c r="P64" s="8"/>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:16">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
       <c r="I65" s="9"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10"/>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="11"/>
+      <c r="O65" s="11"/>
+      <c r="P65" s="11"/>
     </row>
     <row r="66" s="2" customFormat="1" spans="1:16">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
       <c r="I66" s="9"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="11"/>
-      <c r="P66" s="11"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="12"/>
+      <c r="P66" s="12"/>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="9"/>
       <c r="B67" s="9"/>
-      <c r="C67" s="12"/>
+      <c r="C67" s="13"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
       <c r="G67" s="9"/>
@@ -3207,7 +3209,7 @@
     <row r="68" spans="1:16">
       <c r="A68" s="9"/>
       <c r="B68" s="9"/>
-      <c r="C68" s="12"/>
+      <c r="C68" s="13"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
       <c r="G68" s="9"/>
@@ -3224,7 +3226,7 @@
     <row r="69" spans="1:16">
       <c r="A69" s="9"/>
       <c r="B69" s="9"/>
-      <c r="C69" s="12"/>
+      <c r="C69" s="13"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
       <c r="G69" s="9"/>
@@ -3241,7 +3243,7 @@
     <row r="70" spans="1:16">
       <c r="A70" s="9"/>
       <c r="B70" s="9"/>
-      <c r="C70" s="12"/>
+      <c r="C70" s="13"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
       <c r="G70" s="9"/>
@@ -3258,7 +3260,7 @@
     <row r="71" spans="1:16">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
-      <c r="C71" s="12"/>
+      <c r="C71" s="13"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
       <c r="G71" s="9"/>
@@ -3275,7 +3277,7 @@
     <row r="72" spans="1:16">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
-      <c r="C72" s="12"/>
+      <c r="C72" s="13"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
       <c r="G72" s="9"/>
@@ -3292,7 +3294,7 @@
     <row r="73" spans="1:16">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
-      <c r="C73" s="12"/>
+      <c r="C73" s="13"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
       <c r="G73" s="9"/>
@@ -3309,7 +3311,7 @@
     <row r="74" spans="1:16">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
-      <c r="C74" s="12"/>
+      <c r="C74" s="13"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
       <c r="G74" s="9"/>
@@ -3326,7 +3328,7 @@
     <row r="75" spans="1:16">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
-      <c r="C75" s="12"/>
+      <c r="C75" s="13"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
       <c r="G75" s="9"/>
@@ -3343,7 +3345,7 @@
     <row r="76" spans="1:16">
       <c r="A76" s="9"/>
       <c r="B76" s="9"/>
-      <c r="C76" s="12"/>
+      <c r="C76" s="13"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
       <c r="G76" s="9"/>
@@ -3360,7 +3362,7 @@
     <row r="77" spans="1:16">
       <c r="A77" s="9"/>
       <c r="B77" s="9"/>
-      <c r="C77" s="12"/>
+      <c r="C77" s="13"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
       <c r="G77" s="9"/>
@@ -3377,7 +3379,7 @@
     <row r="78" spans="1:16">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
-      <c r="C78" s="12"/>
+      <c r="C78" s="13"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
       <c r="G78" s="9"/>
@@ -3394,7 +3396,7 @@
     <row r="79" spans="1:16">
       <c r="A79" s="9"/>
       <c r="B79" s="9"/>
-      <c r="C79" s="12"/>
+      <c r="C79" s="13"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
       <c r="G79" s="9"/>
@@ -3411,7 +3413,7 @@
     <row r="80" spans="1:16">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
-      <c r="C80" s="12"/>
+      <c r="C80" s="13"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
       <c r="G80" s="9"/>
@@ -3428,7 +3430,7 @@
     <row r="81" spans="1:16">
       <c r="A81" s="9"/>
       <c r="B81" s="9"/>
-      <c r="C81" s="12"/>
+      <c r="C81" s="13"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
       <c r="G81" s="9"/>
@@ -3445,7 +3447,7 @@
     <row r="82" spans="1:16">
       <c r="A82" s="9"/>
       <c r="B82" s="9"/>
-      <c r="C82" s="12"/>
+      <c r="C82" s="13"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
       <c r="G82" s="9"/>
@@ -3462,7 +3464,7 @@
     <row r="83" spans="1:16">
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
-      <c r="C83" s="12"/>
+      <c r="C83" s="13"/>
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
       <c r="G83" s="9"/>
@@ -3479,7 +3481,7 @@
     <row r="84" spans="1:16">
       <c r="A84" s="9"/>
       <c r="B84" s="9"/>
-      <c r="C84" s="12"/>
+      <c r="C84" s="13"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
       <c r="G84" s="9"/>
@@ -3496,7 +3498,7 @@
     <row r="85" spans="1:16">
       <c r="A85" s="9"/>
       <c r="B85" s="9"/>
-      <c r="C85" s="12"/>
+      <c r="C85" s="13"/>
       <c r="D85" s="9"/>
       <c r="E85" s="9"/>
       <c r="G85" s="9"/>
@@ -3513,7 +3515,7 @@
     <row r="86" spans="1:16">
       <c r="A86" s="9"/>
       <c r="B86" s="9"/>
-      <c r="C86" s="12"/>
+      <c r="C86" s="13"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
       <c r="G86" s="9"/>
@@ -3530,7 +3532,7 @@
     <row r="87" spans="1:16">
       <c r="A87" s="9"/>
       <c r="B87" s="9"/>
-      <c r="C87" s="12"/>
+      <c r="C87" s="13"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
       <c r="G87" s="9"/>
@@ -3547,7 +3549,7 @@
     <row r="88" spans="1:16">
       <c r="A88" s="9"/>
       <c r="B88" s="9"/>
-      <c r="C88" s="12"/>
+      <c r="C88" s="13"/>
       <c r="D88" s="9"/>
       <c r="E88" s="9"/>
       <c r="G88" s="9"/>
@@ -3564,7 +3566,7 @@
     <row r="89" spans="1:16">
       <c r="A89" s="9"/>
       <c r="B89" s="9"/>
-      <c r="C89" s="12"/>
+      <c r="C89" s="13"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
       <c r="G89" s="9"/>
@@ -3581,7 +3583,7 @@
     <row r="90" spans="1:16">
       <c r="A90" s="9"/>
       <c r="B90" s="9"/>
-      <c r="C90" s="12"/>
+      <c r="C90" s="13"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
       <c r="G90" s="9"/>
@@ -3598,7 +3600,7 @@
     <row r="91" spans="1:16">
       <c r="A91" s="9"/>
       <c r="B91" s="9"/>
-      <c r="C91" s="12"/>
+      <c r="C91" s="13"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
       <c r="G91" s="9"/>
@@ -3615,7 +3617,7 @@
     <row r="92" spans="1:16">
       <c r="A92" s="9"/>
       <c r="B92" s="9"/>
-      <c r="C92" s="12"/>
+      <c r="C92" s="13"/>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
       <c r="G92" s="9"/>
@@ -3632,7 +3634,7 @@
     <row r="93" spans="1:16">
       <c r="A93" s="9"/>
       <c r="B93" s="9"/>
-      <c r="C93" s="12"/>
+      <c r="C93" s="13"/>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
       <c r="G93" s="9"/>
@@ -3649,7 +3651,7 @@
     <row r="94" spans="1:16">
       <c r="A94" s="9"/>
       <c r="B94" s="9"/>
-      <c r="C94" s="12"/>
+      <c r="C94" s="13"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
       <c r="G94" s="9"/>
@@ -3666,7 +3668,7 @@
     <row r="95" spans="1:16">
       <c r="A95" s="9"/>
       <c r="B95" s="9"/>
-      <c r="C95" s="12"/>
+      <c r="C95" s="13"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
       <c r="G95" s="9"/>
@@ -3683,7 +3685,7 @@
     <row r="96" spans="1:16">
       <c r="A96" s="9"/>
       <c r="B96" s="9"/>
-      <c r="C96" s="12"/>
+      <c r="C96" s="13"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
       <c r="G96" s="9"/>
@@ -3700,7 +3702,7 @@
     <row r="97" spans="1:16">
       <c r="A97" s="9"/>
       <c r="B97" s="9"/>
-      <c r="C97" s="12"/>
+      <c r="C97" s="13"/>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
       <c r="G97" s="9"/>
@@ -3717,7 +3719,7 @@
     <row r="98" spans="1:16">
       <c r="A98" s="9"/>
       <c r="B98" s="9"/>
-      <c r="C98" s="12"/>
+      <c r="C98" s="13"/>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
       <c r="G98" s="9"/>
@@ -3734,7 +3736,7 @@
     <row r="99" spans="1:16">
       <c r="A99" s="9"/>
       <c r="B99" s="9"/>
-      <c r="C99" s="12"/>
+      <c r="C99" s="13"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
       <c r="G99" s="9"/>
@@ -3751,7 +3753,7 @@
     <row r="100" spans="1:16">
       <c r="A100" s="9"/>
       <c r="B100" s="9"/>
-      <c r="C100" s="12"/>
+      <c r="C100" s="13"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
       <c r="G100" s="9"/>
@@ -3768,7 +3770,7 @@
     <row r="101" spans="1:16">
       <c r="A101" s="9"/>
       <c r="B101" s="9"/>
-      <c r="C101" s="12"/>
+      <c r="C101" s="13"/>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
       <c r="G101" s="9"/>
@@ -3785,7 +3787,7 @@
     <row r="102" spans="1:16">
       <c r="A102" s="9"/>
       <c r="B102" s="9"/>
-      <c r="C102" s="12"/>
+      <c r="C102" s="13"/>
       <c r="D102" s="9"/>
       <c r="E102" s="9"/>
       <c r="G102" s="9"/>
@@ -3802,7 +3804,7 @@
     <row r="103" spans="1:16">
       <c r="A103" s="9"/>
       <c r="B103" s="9"/>
-      <c r="C103" s="12"/>
+      <c r="C103" s="13"/>
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
       <c r="G103" s="9"/>
@@ -3819,7 +3821,7 @@
     <row r="104" spans="1:16">
       <c r="A104" s="9"/>
       <c r="B104" s="9"/>
-      <c r="C104" s="12"/>
+      <c r="C104" s="13"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
       <c r="G104" s="9"/>
@@ -3836,7 +3838,7 @@
     <row r="105" spans="1:16">
       <c r="A105" s="9"/>
       <c r="B105" s="9"/>
-      <c r="C105" s="12"/>
+      <c r="C105" s="13"/>
       <c r="D105" s="9"/>
       <c r="E105" s="9"/>
       <c r="G105" s="9"/>
@@ -3853,7 +3855,7 @@
     <row r="106" spans="1:16">
       <c r="A106" s="9"/>
       <c r="B106" s="9"/>
-      <c r="C106" s="12"/>
+      <c r="C106" s="13"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
       <c r="G106" s="9"/>
@@ -3870,7 +3872,7 @@
     <row r="107" spans="1:16">
       <c r="A107" s="9"/>
       <c r="B107" s="9"/>
-      <c r="C107" s="12"/>
+      <c r="C107" s="13"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
       <c r="G107" s="9"/>
@@ -3887,7 +3889,7 @@
     <row r="108" spans="1:16">
       <c r="A108" s="9"/>
       <c r="B108" s="9"/>
-      <c r="C108" s="12"/>
+      <c r="C108" s="13"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
       <c r="G108" s="9"/>
@@ -3904,7 +3906,7 @@
     <row r="109" spans="1:16">
       <c r="A109" s="9"/>
       <c r="B109" s="9"/>
-      <c r="C109" s="12"/>
+      <c r="C109" s="13"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
       <c r="G109" s="9"/>
@@ -3921,7 +3923,7 @@
     <row r="110" spans="1:16">
       <c r="A110" s="9"/>
       <c r="B110" s="9"/>
-      <c r="C110" s="12"/>
+      <c r="C110" s="13"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
       <c r="G110" s="9"/>
@@ -3938,7 +3940,7 @@
     <row r="111" spans="1:16">
       <c r="A111" s="9"/>
       <c r="B111" s="9"/>
-      <c r="C111" s="12"/>
+      <c r="C111" s="13"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
       <c r="G111" s="9"/>
@@ -3955,7 +3957,7 @@
     <row r="112" spans="1:16">
       <c r="A112" s="9"/>
       <c r="B112" s="9"/>
-      <c r="C112" s="12"/>
+      <c r="C112" s="13"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
       <c r="G112" s="9"/>
@@ -3972,7 +3974,7 @@
     <row r="113" spans="1:16">
       <c r="A113" s="9"/>
       <c r="B113" s="9"/>
-      <c r="C113" s="12"/>
+      <c r="C113" s="13"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
       <c r="G113" s="9"/>
@@ -3989,7 +3991,7 @@
     <row r="114" spans="1:16">
       <c r="A114" s="9"/>
       <c r="B114" s="9"/>
-      <c r="C114" s="12"/>
+      <c r="C114" s="13"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
       <c r="G114" s="9"/>
@@ -4006,7 +4008,7 @@
     <row r="115" spans="1:16">
       <c r="A115" s="9"/>
       <c r="B115" s="9"/>
-      <c r="C115" s="12"/>
+      <c r="C115" s="13"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
       <c r="G115" s="9"/>
@@ -4023,7 +4025,7 @@
     <row r="116" spans="1:16">
       <c r="A116" s="9"/>
       <c r="B116" s="9"/>
-      <c r="C116" s="12"/>
+      <c r="C116" s="13"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
       <c r="G116" s="9"/>
@@ -4040,7 +4042,7 @@
     <row r="117" spans="1:16">
       <c r="A117" s="9"/>
       <c r="B117" s="9"/>
-      <c r="C117" s="12"/>
+      <c r="C117" s="13"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
       <c r="G117" s="9"/>
@@ -4057,7 +4059,7 @@
     <row r="118" spans="1:16">
       <c r="A118" s="9"/>
       <c r="B118" s="9"/>
-      <c r="C118" s="12"/>
+      <c r="C118" s="13"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
       <c r="G118" s="9"/>
@@ -4074,7 +4076,7 @@
     <row r="119" spans="1:16">
       <c r="A119" s="9"/>
       <c r="B119" s="9"/>
-      <c r="C119" s="12"/>
+      <c r="C119" s="13"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
       <c r="G119" s="9"/>
@@ -4091,7 +4093,7 @@
     <row r="120" spans="1:16">
       <c r="A120" s="9"/>
       <c r="B120" s="9"/>
-      <c r="C120" s="12"/>
+      <c r="C120" s="13"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
       <c r="G120" s="9"/>
@@ -4108,7 +4110,7 @@
     <row r="121" spans="1:16">
       <c r="A121" s="9"/>
       <c r="B121" s="9"/>
-      <c r="C121" s="12"/>
+      <c r="C121" s="13"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
       <c r="G121" s="9"/>
@@ -4125,7 +4127,7 @@
     <row r="122" spans="1:16">
       <c r="A122" s="9"/>
       <c r="B122" s="9"/>
-      <c r="C122" s="12"/>
+      <c r="C122" s="13"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
       <c r="G122" s="9"/>
@@ -4142,7 +4144,7 @@
     <row r="123" spans="1:16">
       <c r="A123" s="9"/>
       <c r="B123" s="9"/>
-      <c r="C123" s="12"/>
+      <c r="C123" s="13"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
       <c r="G123" s="9"/>
@@ -4159,7 +4161,7 @@
     <row r="124" spans="1:16">
       <c r="A124" s="9"/>
       <c r="B124" s="9"/>
-      <c r="C124" s="12"/>
+      <c r="C124" s="13"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
       <c r="G124" s="9"/>
@@ -4176,7 +4178,7 @@
     <row r="125" spans="1:16">
       <c r="A125" s="9"/>
       <c r="B125" s="9"/>
-      <c r="C125" s="12"/>
+      <c r="C125" s="13"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
       <c r="G125" s="9"/>
@@ -4193,7 +4195,7 @@
     <row r="126" spans="1:16">
       <c r="A126" s="9"/>
       <c r="B126" s="9"/>
-      <c r="C126" s="12"/>
+      <c r="C126" s="13"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
       <c r="G126" s="9"/>
@@ -4210,7 +4212,7 @@
     <row r="127" spans="1:16">
       <c r="A127" s="9"/>
       <c r="B127" s="9"/>
-      <c r="C127" s="12"/>
+      <c r="C127" s="13"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
       <c r="G127" s="9"/>
@@ -4227,7 +4229,7 @@
     <row r="128" spans="1:16">
       <c r="A128" s="9"/>
       <c r="B128" s="9"/>
-      <c r="C128" s="12"/>
+      <c r="C128" s="13"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
       <c r="G128" s="9"/>
@@ -4244,7 +4246,7 @@
     <row r="129" spans="1:16">
       <c r="A129" s="9"/>
       <c r="B129" s="9"/>
-      <c r="C129" s="12"/>
+      <c r="C129" s="13"/>
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
       <c r="G129" s="9"/>
@@ -4261,7 +4263,7 @@
     <row r="130" spans="1:16">
       <c r="A130" s="9"/>
       <c r="B130" s="9"/>
-      <c r="C130" s="12"/>
+      <c r="C130" s="13"/>
       <c r="D130" s="9"/>
       <c r="E130" s="9"/>
       <c r="G130" s="9"/>
@@ -4278,7 +4280,7 @@
     <row r="131" spans="1:16">
       <c r="A131" s="9"/>
       <c r="B131" s="9"/>
-      <c r="C131" s="12"/>
+      <c r="C131" s="13"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
       <c r="G131" s="9"/>
@@ -4295,7 +4297,7 @@
     <row r="132" spans="1:16">
       <c r="A132" s="9"/>
       <c r="B132" s="9"/>
-      <c r="C132" s="12"/>
+      <c r="C132" s="13"/>
       <c r="D132" s="9"/>
       <c r="E132" s="9"/>
       <c r="G132" s="9"/>
@@ -4312,7 +4314,7 @@
     <row r="133" spans="1:16">
       <c r="A133" s="9"/>
       <c r="B133" s="9"/>
-      <c r="C133" s="12"/>
+      <c r="C133" s="13"/>
       <c r="D133" s="9"/>
       <c r="E133" s="9"/>
       <c r="G133" s="9"/>
@@ -4329,7 +4331,7 @@
     <row r="134" spans="1:16">
       <c r="A134" s="9"/>
       <c r="B134" s="9"/>
-      <c r="C134" s="12"/>
+      <c r="C134" s="13"/>
       <c r="D134" s="9"/>
       <c r="E134" s="9"/>
       <c r="G134" s="9"/>
@@ -4346,7 +4348,7 @@
     <row r="135" spans="1:16">
       <c r="A135" s="9"/>
       <c r="B135" s="9"/>
-      <c r="C135" s="12"/>
+      <c r="C135" s="13"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
       <c r="G135" s="9"/>
@@ -4363,7 +4365,7 @@
     <row r="136" spans="1:16">
       <c r="A136" s="9"/>
       <c r="B136" s="9"/>
-      <c r="C136" s="12"/>
+      <c r="C136" s="13"/>
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
       <c r="G136" s="9"/>
@@ -4380,7 +4382,7 @@
     <row r="137" spans="1:16">
       <c r="A137" s="9"/>
       <c r="B137" s="9"/>
-      <c r="C137" s="12"/>
+      <c r="C137" s="13"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
       <c r="G137" s="9"/>
@@ -4397,7 +4399,7 @@
     <row r="138" spans="1:16">
       <c r="A138" s="9"/>
       <c r="B138" s="9"/>
-      <c r="C138" s="12"/>
+      <c r="C138" s="13"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
       <c r="G138" s="9"/>
@@ -4414,7 +4416,7 @@
     <row r="139" spans="1:16">
       <c r="A139" s="9"/>
       <c r="B139" s="9"/>
-      <c r="C139" s="12"/>
+      <c r="C139" s="13"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
       <c r="G139" s="9"/>
@@ -4431,7 +4433,7 @@
     <row r="140" spans="1:16">
       <c r="A140" s="9"/>
       <c r="B140" s="9"/>
-      <c r="C140" s="12"/>
+      <c r="C140" s="13"/>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
       <c r="G140" s="9"/>
@@ -4448,7 +4450,7 @@
     <row r="141" spans="1:16">
       <c r="A141" s="9"/>
       <c r="B141" s="9"/>
-      <c r="C141" s="12"/>
+      <c r="C141" s="13"/>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
       <c r="G141" s="9"/>
@@ -4465,7 +4467,7 @@
     <row r="142" spans="1:16">
       <c r="A142" s="9"/>
       <c r="B142" s="9"/>
-      <c r="C142" s="12"/>
+      <c r="C142" s="13"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
       <c r="G142" s="9"/>
@@ -4482,7 +4484,7 @@
     <row r="143" spans="1:16">
       <c r="A143" s="9"/>
       <c r="B143" s="9"/>
-      <c r="C143" s="12"/>
+      <c r="C143" s="13"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
       <c r="G143" s="9"/>
@@ -4499,7 +4501,7 @@
     <row r="144" spans="1:16">
       <c r="A144" s="9"/>
       <c r="B144" s="9"/>
-      <c r="C144" s="12"/>
+      <c r="C144" s="13"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
       <c r="G144" s="9"/>
@@ -4516,7 +4518,7 @@
     <row r="145" spans="1:16">
       <c r="A145" s="9"/>
       <c r="B145" s="9"/>
-      <c r="C145" s="12"/>
+      <c r="C145" s="13"/>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
       <c r="G145" s="9"/>
@@ -4533,7 +4535,7 @@
     <row r="146" spans="1:16">
       <c r="A146" s="9"/>
       <c r="B146" s="9"/>
-      <c r="C146" s="12"/>
+      <c r="C146" s="13"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
       <c r="G146" s="9"/>
@@ -4550,7 +4552,7 @@
     <row r="147" spans="1:16">
       <c r="A147" s="9"/>
       <c r="B147" s="9"/>
-      <c r="C147" s="12"/>
+      <c r="C147" s="13"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
       <c r="G147" s="9"/>
@@ -4567,7 +4569,7 @@
     <row r="148" spans="1:16">
       <c r="A148" s="9"/>
       <c r="B148" s="9"/>
-      <c r="C148" s="12"/>
+      <c r="C148" s="13"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
       <c r="G148" s="9"/>
@@ -4584,7 +4586,7 @@
     <row r="149" spans="1:16">
       <c r="A149" s="9"/>
       <c r="B149" s="9"/>
-      <c r="C149" s="12"/>
+      <c r="C149" s="13"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
       <c r="G149" s="9"/>
@@ -4601,7 +4603,7 @@
     <row r="150" spans="1:16">
       <c r="A150" s="9"/>
       <c r="B150" s="9"/>
-      <c r="C150" s="12"/>
+      <c r="C150" s="13"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
       <c r="G150" s="9"/>
@@ -4618,7 +4620,7 @@
     <row r="151" spans="1:16">
       <c r="A151" s="9"/>
       <c r="B151" s="9"/>
-      <c r="C151" s="12"/>
+      <c r="C151" s="13"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
       <c r="G151" s="9"/>
@@ -4635,7 +4637,7 @@
     <row r="152" spans="1:16">
       <c r="A152" s="9"/>
       <c r="B152" s="9"/>
-      <c r="C152" s="12"/>
+      <c r="C152" s="13"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
       <c r="G152" s="9"/>
@@ -4652,7 +4654,7 @@
     <row r="153" spans="1:16">
       <c r="A153" s="9"/>
       <c r="B153" s="9"/>
-      <c r="C153" s="12"/>
+      <c r="C153" s="13"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
       <c r="G153" s="9"/>
@@ -4669,7 +4671,7 @@
     <row r="154" spans="1:16">
       <c r="A154" s="9"/>
       <c r="B154" s="9"/>
-      <c r="C154" s="12"/>
+      <c r="C154" s="13"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
       <c r="G154" s="9"/>
@@ -4686,7 +4688,7 @@
     <row r="155" spans="1:16">
       <c r="A155" s="9"/>
       <c r="B155" s="9"/>
-      <c r="C155" s="12"/>
+      <c r="C155" s="13"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
       <c r="G155" s="9"/>
@@ -4703,7 +4705,7 @@
     <row r="156" spans="1:16">
       <c r="A156" s="9"/>
       <c r="B156" s="9"/>
-      <c r="C156" s="12"/>
+      <c r="C156" s="13"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
       <c r="G156" s="9"/>
@@ -4720,7 +4722,7 @@
     <row r="157" spans="1:16">
       <c r="A157" s="9"/>
       <c r="B157" s="9"/>
-      <c r="C157" s="12"/>
+      <c r="C157" s="13"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
       <c r="G157" s="9"/>
@@ -4737,7 +4739,7 @@
     <row r="158" spans="1:16">
       <c r="A158" s="9"/>
       <c r="B158" s="9"/>
-      <c r="C158" s="12"/>
+      <c r="C158" s="13"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
       <c r="G158" s="9"/>
@@ -4754,7 +4756,7 @@
     <row r="159" spans="1:16">
       <c r="A159" s="9"/>
       <c r="B159" s="9"/>
-      <c r="C159" s="12"/>
+      <c r="C159" s="13"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
       <c r="G159" s="9"/>
@@ -4771,7 +4773,7 @@
     <row r="160" spans="1:16">
       <c r="A160" s="9"/>
       <c r="B160" s="9"/>
-      <c r="C160" s="12"/>
+      <c r="C160" s="13"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
       <c r="G160" s="9"/>
@@ -4788,7 +4790,7 @@
     <row r="161" spans="1:16">
       <c r="A161" s="9"/>
       <c r="B161" s="9"/>
-      <c r="C161" s="12"/>
+      <c r="C161" s="13"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
       <c r="G161" s="9"/>
@@ -4805,7 +4807,7 @@
     <row r="162" spans="1:16">
       <c r="A162" s="9"/>
       <c r="B162" s="9"/>
-      <c r="C162" s="12"/>
+      <c r="C162" s="13"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
       <c r="G162" s="9"/>
@@ -4822,7 +4824,7 @@
     <row r="163" spans="1:16">
       <c r="A163" s="9"/>
       <c r="B163" s="9"/>
-      <c r="C163" s="12"/>
+      <c r="C163" s="13"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
       <c r="G163" s="9"/>
@@ -4839,7 +4841,7 @@
     <row r="164" spans="1:16">
       <c r="A164" s="9"/>
       <c r="B164" s="9"/>
-      <c r="C164" s="12"/>
+      <c r="C164" s="13"/>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
       <c r="F164" s="9"/>
@@ -4857,7 +4859,7 @@
     <row r="165" spans="1:16">
       <c r="A165" s="9"/>
       <c r="B165" s="9"/>
-      <c r="C165" s="12"/>
+      <c r="C165" s="13"/>
       <c r="D165" s="9"/>
       <c r="E165" s="9"/>
       <c r="F165" s="9"/>
@@ -4875,7 +4877,7 @@
     <row r="166" spans="1:16">
       <c r="A166" s="9"/>
       <c r="B166" s="9"/>
-      <c r="C166" s="12"/>
+      <c r="C166" s="13"/>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
       <c r="F166" s="9"/>
@@ -4893,7 +4895,7 @@
     <row r="167" spans="1:16">
       <c r="A167" s="9"/>
       <c r="B167" s="9"/>
-      <c r="C167" s="12"/>
+      <c r="C167" s="13"/>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
       <c r="F167" s="9"/>
@@ -4911,7 +4913,7 @@
     <row r="168" spans="1:16">
       <c r="A168" s="9"/>
       <c r="B168" s="9"/>
-      <c r="C168" s="12"/>
+      <c r="C168" s="13"/>
       <c r="D168" s="9"/>
       <c r="E168" s="9"/>
       <c r="F168" s="9"/>
@@ -4929,7 +4931,7 @@
     <row r="169" spans="1:16">
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
-      <c r="C169" s="12"/>
+      <c r="C169" s="13"/>
       <c r="D169" s="9"/>
       <c r="E169" s="9"/>
       <c r="F169" s="9"/>
@@ -4947,7 +4949,7 @@
     <row r="170" spans="1:16">
       <c r="A170" s="9"/>
       <c r="B170" s="9"/>
-      <c r="C170" s="12"/>
+      <c r="C170" s="13"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
       <c r="F170" s="9"/>
@@ -4965,7 +4967,7 @@
     <row r="171" spans="1:16">
       <c r="A171" s="9"/>
       <c r="B171" s="9"/>
-      <c r="C171" s="12"/>
+      <c r="C171" s="13"/>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
       <c r="F171" s="9"/>
@@ -4983,7 +4985,7 @@
     <row r="172" spans="1:16">
       <c r="A172" s="9"/>
       <c r="B172" s="9"/>
-      <c r="C172" s="12"/>
+      <c r="C172" s="13"/>
       <c r="D172" s="9"/>
       <c r="E172" s="9"/>
       <c r="F172" s="9"/>
@@ -5001,7 +5003,7 @@
     <row r="173" spans="1:16">
       <c r="A173" s="9"/>
       <c r="B173" s="9"/>
-      <c r="C173" s="12"/>
+      <c r="C173" s="13"/>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
       <c r="F173" s="9"/>
@@ -5019,7 +5021,7 @@
     <row r="174" spans="1:16">
       <c r="A174" s="9"/>
       <c r="B174" s="9"/>
-      <c r="C174" s="12"/>
+      <c r="C174" s="13"/>
       <c r="D174" s="9"/>
       <c r="E174" s="9"/>
       <c r="F174" s="9"/>
@@ -5037,7 +5039,7 @@
     <row r="175" spans="1:16">
       <c r="A175" s="9"/>
       <c r="B175" s="9"/>
-      <c r="C175" s="12"/>
+      <c r="C175" s="13"/>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
       <c r="F175" s="9"/>
@@ -5055,7 +5057,7 @@
     <row r="176" spans="1:16">
       <c r="A176" s="9"/>
       <c r="B176" s="9"/>
-      <c r="C176" s="12"/>
+      <c r="C176" s="13"/>
       <c r="D176" s="9"/>
       <c r="E176" s="9"/>
       <c r="F176" s="9"/>
@@ -5073,7 +5075,7 @@
     <row r="177" spans="1:16">
       <c r="A177" s="9"/>
       <c r="B177" s="9"/>
-      <c r="C177" s="12"/>
+      <c r="C177" s="13"/>
       <c r="D177" s="9"/>
       <c r="E177" s="9"/>
       <c r="F177" s="9"/>
@@ -5091,7 +5093,7 @@
     <row r="178" spans="1:16">
       <c r="A178" s="9"/>
       <c r="B178" s="9"/>
-      <c r="C178" s="12"/>
+      <c r="C178" s="13"/>
       <c r="D178" s="9"/>
       <c r="E178" s="9"/>
       <c r="F178" s="9"/>
@@ -5109,7 +5111,7 @@
     <row r="179" spans="1:16">
       <c r="A179" s="9"/>
       <c r="B179" s="9"/>
-      <c r="C179" s="12"/>
+      <c r="C179" s="13"/>
       <c r="D179" s="9"/>
       <c r="E179" s="9"/>
       <c r="F179" s="9"/>
@@ -5127,7 +5129,7 @@
     <row r="180" spans="1:16">
       <c r="A180" s="9"/>
       <c r="B180" s="9"/>
-      <c r="C180" s="12"/>
+      <c r="C180" s="13"/>
       <c r="D180" s="9"/>
       <c r="E180" s="9"/>
       <c r="F180" s="9"/>
@@ -5145,7 +5147,7 @@
     <row r="181" spans="1:16">
       <c r="A181" s="9"/>
       <c r="B181" s="9"/>
-      <c r="C181" s="12"/>
+      <c r="C181" s="13"/>
       <c r="D181" s="9"/>
       <c r="E181" s="9"/>
       <c r="F181" s="9"/>
@@ -5163,7 +5165,7 @@
     <row r="182" spans="1:16">
       <c r="A182" s="9"/>
       <c r="B182" s="9"/>
-      <c r="C182" s="12"/>
+      <c r="C182" s="13"/>
       <c r="D182" s="9"/>
       <c r="E182" s="9"/>
       <c r="F182" s="9"/>
@@ -5181,7 +5183,7 @@
     <row r="183" spans="1:16">
       <c r="A183" s="9"/>
       <c r="B183" s="9"/>
-      <c r="C183" s="12"/>
+      <c r="C183" s="13"/>
       <c r="D183" s="9"/>
       <c r="E183" s="9"/>
       <c r="F183" s="9"/>
@@ -5199,7 +5201,7 @@
     <row r="184" spans="1:16">
       <c r="A184" s="9"/>
       <c r="B184" s="9"/>
-      <c r="C184" s="12"/>
+      <c r="C184" s="13"/>
       <c r="D184" s="9"/>
       <c r="E184" s="9"/>
       <c r="F184" s="9"/>
@@ -5217,7 +5219,7 @@
     <row r="185" spans="1:16">
       <c r="A185" s="9"/>
       <c r="B185" s="9"/>
-      <c r="C185" s="12"/>
+      <c r="C185" s="13"/>
       <c r="D185" s="9"/>
       <c r="E185" s="9"/>
       <c r="F185" s="9"/>
@@ -5235,7 +5237,7 @@
     <row r="186" spans="1:16">
       <c r="A186" s="9"/>
       <c r="B186" s="9"/>
-      <c r="C186" s="12"/>
+      <c r="C186" s="13"/>
       <c r="D186" s="9"/>
       <c r="E186" s="9"/>
       <c r="F186" s="9"/>
@@ -5253,7 +5255,7 @@
     <row r="187" spans="1:16">
       <c r="A187" s="9"/>
       <c r="B187" s="9"/>
-      <c r="C187" s="12"/>
+      <c r="C187" s="13"/>
       <c r="D187" s="9"/>
       <c r="E187" s="9"/>
       <c r="F187" s="9"/>
@@ -5271,7 +5273,7 @@
     <row r="188" spans="1:16">
       <c r="A188" s="9"/>
       <c r="B188" s="9"/>
-      <c r="C188" s="12"/>
+      <c r="C188" s="13"/>
       <c r="D188" s="9"/>
       <c r="E188" s="9"/>
       <c r="F188" s="9"/>
@@ -5286,10 +5288,10 @@
       <c r="O188" s="9"/>
       <c r="P188" s="9"/>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" ht="14.75" spans="1:16">
       <c r="A189" s="9"/>
       <c r="B189" s="9"/>
-      <c r="C189" s="12"/>
+      <c r="C189" s="13"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
       <c r="F189" s="9"/>
@@ -5304,50 +5306,50 @@
       <c r="O189" s="9"/>
       <c r="P189" s="9"/>
     </row>
-    <row r="190" spans="1:13">
-      <c r="A190" s="13"/>
-      <c r="B190" s="13"/>
-      <c r="C190" s="13"/>
-      <c r="D190" s="13"/>
-      <c r="E190" s="13"/>
-      <c r="F190" s="13"/>
-      <c r="G190" s="13"/>
-      <c r="H190" s="13"/>
-      <c r="I190" s="13"/>
-      <c r="J190" s="13"/>
-      <c r="K190" s="13"/>
-      <c r="L190" s="13"/>
-      <c r="M190" s="13"/>
-    </row>
-    <row r="191" spans="1:13">
-      <c r="A191" s="13"/>
-      <c r="B191" s="13"/>
-      <c r="C191" s="13"/>
-      <c r="D191" s="13"/>
-      <c r="E191" s="13"/>
-      <c r="F191" s="13"/>
-      <c r="G191" s="13"/>
-      <c r="H191" s="13"/>
-      <c r="I191" s="13"/>
-      <c r="J191" s="13"/>
-      <c r="K191" s="13"/>
-      <c r="L191" s="13"/>
-      <c r="M191" s="13"/>
-    </row>
-    <row r="192" spans="1:13">
-      <c r="A192" s="13"/>
-      <c r="B192" s="13"/>
-      <c r="C192" s="13"/>
-      <c r="D192" s="13"/>
-      <c r="E192" s="13"/>
-      <c r="F192" s="13"/>
-      <c r="G192" s="13"/>
-      <c r="H192" s="13"/>
-      <c r="I192" s="13"/>
-      <c r="J192" s="13"/>
-      <c r="K192" s="13"/>
-      <c r="L192" s="13"/>
-      <c r="M192" s="13"/>
+    <row r="190" ht="14.75" spans="1:16">
+      <c r="A190" s="14"/>
+      <c r="B190" s="14"/>
+      <c r="C190" s="14"/>
+      <c r="D190" s="14"/>
+      <c r="E190" s="14"/>
+      <c r="F190" s="14"/>
+      <c r="G190" s="14"/>
+      <c r="H190" s="14"/>
+      <c r="I190" s="14"/>
+      <c r="J190" s="14"/>
+      <c r="K190" s="14"/>
+      <c r="L190" s="14"/>
+      <c r="M190" s="14"/>
+    </row>
+    <row r="191" ht="14.75" spans="1:16">
+      <c r="A191" s="14"/>
+      <c r="B191" s="14"/>
+      <c r="C191" s="14"/>
+      <c r="D191" s="14"/>
+      <c r="E191" s="14"/>
+      <c r="F191" s="14"/>
+      <c r="G191" s="14"/>
+      <c r="H191" s="14"/>
+      <c r="I191" s="14"/>
+      <c r="J191" s="14"/>
+      <c r="K191" s="14"/>
+      <c r="L191" s="14"/>
+      <c r="M191" s="14"/>
+    </row>
+    <row r="192" ht="14.75" spans="1:16">
+      <c r="A192" s="14"/>
+      <c r="B192" s="14"/>
+      <c r="C192" s="14"/>
+      <c r="D192" s="14"/>
+      <c r="E192" s="14"/>
+      <c r="F192" s="14"/>
+      <c r="G192" s="14"/>
+      <c r="H192" s="14"/>
+      <c r="I192" s="14"/>
+      <c r="J192" s="14"/>
+      <c r="K192" s="14"/>
+      <c r="L192" s="14"/>
+      <c r="M192" s="14"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P148" etc:filterBottomFollowUsedRange="0">

--- a/Tools/Luban/DataTables/Datas/H_合成.xlsx
+++ b/Tools/Luban/DataTables/Datas/H_合成.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$P$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$P$146</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -143,13 +143,7 @@
     <t>番茄-紫-房子</t>
   </si>
   <si>
-    <t>花椰菜-房子</t>
-  </si>
-  <si>
     <t>猕猴桃-房子</t>
-  </si>
-  <si>
-    <t>野草-房子</t>
   </si>
   <si>
     <t>爆米花-土豆&amp;蘑菇味</t>
@@ -1379,7 +1373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P192"/>
+  <dimension ref="A1:P190"/>
   <sheetFormatPr defaultColWidth="12.1666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="12.1666666666667" style="3"/>
@@ -1835,9 +1829,9 @@
       <c r="P16" s="8"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="9"/>
+      <c r="A17" s="8"/>
       <c r="B17" s="8">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>37</v>
@@ -1846,71 +1840,73 @@
         <v>1</v>
       </c>
       <c r="E17" s="8">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="F17" s="10">
         <v>5045</v>
       </c>
       <c r="G17" s="8">
-        <v>6013</v>
-      </c>
+        <v>6014</v>
+      </c>
+      <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
     </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8">
-        <v>1014</v>
-      </c>
-      <c r="C18" s="8" t="s">
+    <row r="18" s="1" customFormat="1" spans="1:16">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11">
+        <v>2001</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="8">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3014</v>
-      </c>
-      <c r="F18" s="10">
-        <v>5045</v>
-      </c>
-      <c r="G18" s="8">
-        <v>6014</v>
-      </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
+      <c r="D18" s="11">
+        <v>2</v>
+      </c>
+      <c r="E18" s="11">
+        <v>2001</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G18" s="11">
+        <v>5009</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="8"/>
       <c r="B19" s="8">
-        <v>1015</v>
+        <v>2002</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="8">
-        <v>3015</v>
-      </c>
-      <c r="F19" s="10">
-        <v>5045</v>
+        <v>2001</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2003</v>
       </c>
       <c r="G19" s="8">
-        <v>6015</v>
+        <v>5010</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -1922,40 +1918,40 @@
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
     </row>
-    <row r="20" s="1" customFormat="1" spans="1:16">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11">
+    <row r="20" spans="1:16">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8">
+        <v>2003</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="8">
+        <v>2</v>
+      </c>
+      <c r="E20" s="8">
         <v>2001</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="11">
-        <v>2</v>
-      </c>
-      <c r="E20" s="11">
-        <v>2001</v>
-      </c>
-      <c r="F20" s="1">
-        <v>2002</v>
-      </c>
-      <c r="G20" s="11">
-        <v>5009</v>
-      </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
+      <c r="F20" s="3">
+        <v>2004</v>
+      </c>
+      <c r="G20" s="8">
+        <v>5011</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="8"/>
       <c r="B21" s="8">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>41</v>
@@ -1967,10 +1963,10 @@
         <v>2001</v>
       </c>
       <c r="F21" s="3">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="G21" s="8">
-        <v>5010</v>
+        <v>5012</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -1985,7 +1981,7 @@
     <row r="22" spans="1:16">
       <c r="A22" s="8"/>
       <c r="B22" s="8">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>42</v>
@@ -1997,10 +1993,10 @@
         <v>2001</v>
       </c>
       <c r="F22" s="3">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="G22" s="8">
-        <v>5011</v>
+        <v>5013</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -2015,7 +2011,7 @@
     <row r="23" spans="1:16">
       <c r="A23" s="8"/>
       <c r="B23" s="8">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>43</v>
@@ -2027,10 +2023,10 @@
         <v>2001</v>
       </c>
       <c r="F23" s="3">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="G23" s="8">
-        <v>5012</v>
+        <v>5014</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -2045,7 +2041,7 @@
     <row r="24" spans="1:16">
       <c r="A24" s="8"/>
       <c r="B24" s="8">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>44</v>
@@ -2057,10 +2053,10 @@
         <v>2001</v>
       </c>
       <c r="F24" s="3">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="G24" s="8">
-        <v>5013</v>
+        <v>5015</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -2075,7 +2071,7 @@
     <row r="25" spans="1:16">
       <c r="A25" s="8"/>
       <c r="B25" s="8">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>45</v>
@@ -2087,10 +2083,10 @@
         <v>2001</v>
       </c>
       <c r="F25" s="3">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="G25" s="8">
-        <v>5014</v>
+        <v>5016</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -2105,7 +2101,7 @@
     <row r="26" spans="1:16">
       <c r="A26" s="8"/>
       <c r="B26" s="8">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>46</v>
@@ -2114,13 +2110,13 @@
         <v>2</v>
       </c>
       <c r="E26" s="8">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="F26" s="3">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="G26" s="8">
-        <v>5015</v>
+        <v>5017</v>
       </c>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
@@ -2135,7 +2131,7 @@
     <row r="27" spans="1:16">
       <c r="A27" s="8"/>
       <c r="B27" s="8">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>47</v>
@@ -2144,13 +2140,13 @@
         <v>2</v>
       </c>
       <c r="E27" s="8">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="F27" s="3">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="G27" s="8">
-        <v>5016</v>
+        <v>5018</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
@@ -2165,7 +2161,7 @@
     <row r="28" spans="1:16">
       <c r="A28" s="8"/>
       <c r="B28" s="8">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>48</v>
@@ -2177,10 +2173,10 @@
         <v>2002</v>
       </c>
       <c r="F28" s="3">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="G28" s="8">
-        <v>5017</v>
+        <v>5019</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
@@ -2195,7 +2191,7 @@
     <row r="29" spans="1:16">
       <c r="A29" s="8"/>
       <c r="B29" s="8">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>49</v>
@@ -2207,10 +2203,10 @@
         <v>2002</v>
       </c>
       <c r="F29" s="3">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="G29" s="8">
-        <v>5018</v>
+        <v>5020</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
@@ -2225,7 +2221,7 @@
     <row r="30" spans="1:16">
       <c r="A30" s="8"/>
       <c r="B30" s="8">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>50</v>
@@ -2237,10 +2233,10 @@
         <v>2002</v>
       </c>
       <c r="F30" s="3">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="G30" s="8">
-        <v>5019</v>
+        <v>5021</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
@@ -2255,7 +2251,7 @@
     <row r="31" spans="1:16">
       <c r="A31" s="8"/>
       <c r="B31" s="8">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>51</v>
@@ -2267,10 +2263,10 @@
         <v>2002</v>
       </c>
       <c r="F31" s="3">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="G31" s="8">
-        <v>5020</v>
+        <v>5022</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
@@ -2285,7 +2281,7 @@
     <row r="32" spans="1:16">
       <c r="A32" s="8"/>
       <c r="B32" s="8">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>52</v>
@@ -2297,10 +2293,10 @@
         <v>2002</v>
       </c>
       <c r="F32" s="3">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="G32" s="8">
-        <v>5021</v>
+        <v>5023</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
@@ -2315,7 +2311,7 @@
     <row r="33" spans="1:16">
       <c r="A33" s="8"/>
       <c r="B33" s="8">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>53</v>
@@ -2324,13 +2320,13 @@
         <v>2</v>
       </c>
       <c r="E33" s="8">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="F33" s="3">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="G33" s="8">
-        <v>5022</v>
+        <v>5024</v>
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
@@ -2345,7 +2341,7 @@
     <row r="34" spans="1:16">
       <c r="A34" s="8"/>
       <c r="B34" s="8">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>54</v>
@@ -2354,13 +2350,13 @@
         <v>2</v>
       </c>
       <c r="E34" s="8">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="F34" s="3">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="G34" s="8">
-        <v>5023</v>
+        <v>5025</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
@@ -2375,7 +2371,7 @@
     <row r="35" spans="1:16">
       <c r="A35" s="8"/>
       <c r="B35" s="8">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>55</v>
@@ -2387,10 +2383,10 @@
         <v>2003</v>
       </c>
       <c r="F35" s="3">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="G35" s="8">
-        <v>5024</v>
+        <v>5026</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
@@ -2405,7 +2401,7 @@
     <row r="36" spans="1:16">
       <c r="A36" s="8"/>
       <c r="B36" s="8">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>56</v>
@@ -2417,10 +2413,10 @@
         <v>2003</v>
       </c>
       <c r="F36" s="3">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="G36" s="8">
-        <v>5025</v>
+        <v>5027</v>
       </c>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
@@ -2435,7 +2431,7 @@
     <row r="37" spans="1:16">
       <c r="A37" s="8"/>
       <c r="B37" s="8">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>57</v>
@@ -2447,10 +2443,10 @@
         <v>2003</v>
       </c>
       <c r="F37" s="3">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="G37" s="8">
-        <v>5026</v>
+        <v>5028</v>
       </c>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -2465,7 +2461,7 @@
     <row r="38" spans="1:16">
       <c r="A38" s="8"/>
       <c r="B38" s="8">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>58</v>
@@ -2477,10 +2473,10 @@
         <v>2003</v>
       </c>
       <c r="F38" s="3">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="G38" s="8">
-        <v>5027</v>
+        <v>5029</v>
       </c>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
@@ -2495,7 +2491,7 @@
     <row r="39" spans="1:16">
       <c r="A39" s="8"/>
       <c r="B39" s="8">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>59</v>
@@ -2504,13 +2500,13 @@
         <v>2</v>
       </c>
       <c r="E39" s="8">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F39" s="3">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="G39" s="8">
-        <v>5028</v>
+        <v>5030</v>
       </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
@@ -2525,7 +2521,7 @@
     <row r="40" spans="1:16">
       <c r="A40" s="8"/>
       <c r="B40" s="8">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>60</v>
@@ -2534,13 +2530,13 @@
         <v>2</v>
       </c>
       <c r="E40" s="8">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F40" s="3">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="G40" s="8">
-        <v>5029</v>
+        <v>5031</v>
       </c>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
@@ -2555,7 +2551,7 @@
     <row r="41" spans="1:16">
       <c r="A41" s="8"/>
       <c r="B41" s="8">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>61</v>
@@ -2567,10 +2563,10 @@
         <v>2004</v>
       </c>
       <c r="F41" s="3">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="G41" s="8">
-        <v>5030</v>
+        <v>5032</v>
       </c>
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
@@ -2585,7 +2581,7 @@
     <row r="42" spans="1:16">
       <c r="A42" s="8"/>
       <c r="B42" s="8">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>62</v>
@@ -2597,10 +2593,10 @@
         <v>2004</v>
       </c>
       <c r="F42" s="3">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="G42" s="8">
-        <v>5031</v>
+        <v>5033</v>
       </c>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
@@ -2615,7 +2611,7 @@
     <row r="43" spans="1:16">
       <c r="A43" s="8"/>
       <c r="B43" s="8">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>63</v>
@@ -2627,10 +2623,10 @@
         <v>2004</v>
       </c>
       <c r="F43" s="3">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="G43" s="8">
-        <v>5032</v>
+        <v>5034</v>
       </c>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
@@ -2645,7 +2641,7 @@
     <row r="44" spans="1:16">
       <c r="A44" s="8"/>
       <c r="B44" s="8">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>64</v>
@@ -2654,13 +2650,13 @@
         <v>2</v>
       </c>
       <c r="E44" s="8">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="F44" s="3">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="G44" s="8">
-        <v>5033</v>
+        <v>5035</v>
       </c>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
@@ -2675,7 +2671,7 @@
     <row r="45" spans="1:16">
       <c r="A45" s="8"/>
       <c r="B45" s="8">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>65</v>
@@ -2684,13 +2680,13 @@
         <v>2</v>
       </c>
       <c r="E45" s="8">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="F45" s="3">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="G45" s="8">
-        <v>5034</v>
+        <v>5036</v>
       </c>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
@@ -2705,7 +2701,7 @@
     <row r="46" spans="1:16">
       <c r="A46" s="8"/>
       <c r="B46" s="8">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>66</v>
@@ -2717,10 +2713,10 @@
         <v>2005</v>
       </c>
       <c r="F46" s="3">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="G46" s="8">
-        <v>5035</v>
+        <v>5037</v>
       </c>
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
@@ -2735,7 +2731,7 @@
     <row r="47" spans="1:16">
       <c r="A47" s="8"/>
       <c r="B47" s="8">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>67</v>
@@ -2747,10 +2743,10 @@
         <v>2005</v>
       </c>
       <c r="F47" s="3">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="G47" s="8">
-        <v>5036</v>
+        <v>5038</v>
       </c>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
@@ -2765,7 +2761,7 @@
     <row r="48" spans="1:16">
       <c r="A48" s="8"/>
       <c r="B48" s="8">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>68</v>
@@ -2774,16 +2770,16 @@
         <v>2</v>
       </c>
       <c r="E48" s="8">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="F48" s="3">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="G48" s="8">
-        <v>5037</v>
+        <v>5039</v>
       </c>
       <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
+      <c r="I48" s="11"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
@@ -2795,7 +2791,7 @@
     <row r="49" spans="1:16">
       <c r="A49" s="8"/>
       <c r="B49" s="8">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>69</v>
@@ -2804,16 +2800,16 @@
         <v>2</v>
       </c>
       <c r="E49" s="8">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="F49" s="3">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="G49" s="8">
-        <v>5038</v>
+        <v>5040</v>
       </c>
       <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
+      <c r="I49" s="12"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
@@ -2825,7 +2821,7 @@
     <row r="50" spans="1:16">
       <c r="A50" s="8"/>
       <c r="B50" s="8">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>70</v>
@@ -2837,13 +2833,13 @@
         <v>2006</v>
       </c>
       <c r="F50" s="3">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="G50" s="8">
-        <v>5039</v>
+        <v>5041</v>
       </c>
       <c r="H50" s="8"/>
-      <c r="I50" s="11"/>
+      <c r="I50" s="9"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
@@ -2855,7 +2851,7 @@
     <row r="51" spans="1:16">
       <c r="A51" s="8"/>
       <c r="B51" s="8">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>71</v>
@@ -2864,16 +2860,16 @@
         <v>2</v>
       </c>
       <c r="E51" s="8">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="F51" s="3">
         <v>2008</v>
       </c>
       <c r="G51" s="8">
-        <v>5040</v>
+        <v>5042</v>
       </c>
       <c r="H51" s="8"/>
-      <c r="I51" s="12"/>
+      <c r="I51" s="9"/>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
@@ -2885,7 +2881,7 @@
     <row r="52" spans="1:16">
       <c r="A52" s="8"/>
       <c r="B52" s="8">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>72</v>
@@ -2894,13 +2890,13 @@
         <v>2</v>
       </c>
       <c r="E52" s="8">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="F52" s="3">
         <v>2009</v>
       </c>
       <c r="G52" s="8">
-        <v>5041</v>
+        <v>5043</v>
       </c>
       <c r="H52" s="8"/>
       <c r="I52" s="9"/>
@@ -2915,7 +2911,7 @@
     <row r="53" spans="1:16">
       <c r="A53" s="8"/>
       <c r="B53" s="8">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>73</v>
@@ -2924,13 +2920,13 @@
         <v>2</v>
       </c>
       <c r="E53" s="8">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="F53" s="3">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="G53" s="8">
-        <v>5042</v>
+        <v>5044</v>
       </c>
       <c r="H53" s="8"/>
       <c r="I53" s="9"/>
@@ -2944,24 +2940,11 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="8"/>
-      <c r="B54" s="8">
-        <v>2035</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D54" s="8">
-        <v>2</v>
-      </c>
-      <c r="E54" s="8">
-        <v>2007</v>
-      </c>
-      <c r="F54" s="3">
-        <v>2009</v>
-      </c>
-      <c r="G54" s="8">
-        <v>5043</v>
-      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="G54" s="8"/>
       <c r="H54" s="8"/>
       <c r="I54" s="9"/>
       <c r="J54" s="8"/>
@@ -2974,24 +2957,11 @@
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="8"/>
-      <c r="B55" s="8">
-        <v>2036</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D55" s="8">
-        <v>2</v>
-      </c>
-      <c r="E55" s="8">
-        <v>2008</v>
-      </c>
-      <c r="F55" s="3">
-        <v>2009</v>
-      </c>
-      <c r="G55" s="8">
-        <v>5044</v>
-      </c>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="9"/>
       <c r="J55" s="8"/>
@@ -3121,73 +3091,73 @@
       <c r="O62" s="8"/>
       <c r="P62" s="8"/>
     </row>
-    <row r="63" spans="1:16">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
+    <row r="63" s="1" customFormat="1" spans="1:16">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
       <c r="I63" s="9"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="8"/>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
-      <c r="P63" s="8"/>
-    </row>
-    <row r="64" spans="1:16">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+      <c r="N63" s="11"/>
+      <c r="O63" s="11"/>
+      <c r="P63" s="11"/>
+    </row>
+    <row r="64" s="2" customFormat="1" spans="1:16">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
       <c r="I64" s="9"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="8"/>
-      <c r="N64" s="8"/>
-      <c r="O64" s="8"/>
-      <c r="P64" s="8"/>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:16">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
+      <c r="M64" s="12"/>
+      <c r="N64" s="12"/>
+      <c r="O64" s="12"/>
+      <c r="P64" s="12"/>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65" s="9"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
       <c r="I65" s="9"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="11"/>
-      <c r="P65" s="11"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:16">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
+      <c r="M65" s="9"/>
+      <c r="N65" s="9"/>
+      <c r="O65" s="9"/>
+      <c r="P65" s="9"/>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="9"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
       <c r="I66" s="9"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="12"/>
-      <c r="L66" s="12"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="12"/>
-      <c r="O66" s="12"/>
-      <c r="P66" s="12"/>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
+      <c r="N66" s="9"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="9"/>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="9"/>
@@ -4810,6 +4780,7 @@
       <c r="C162" s="13"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
+      <c r="F162" s="9"/>
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="9"/>
@@ -4827,6 +4798,7 @@
       <c r="C163" s="13"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
+      <c r="F163" s="9"/>
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="9"/>
@@ -5252,7 +5224,7 @@
       <c r="O186" s="9"/>
       <c r="P186" s="9"/>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" ht="14.75" spans="1:16">
       <c r="A187" s="9"/>
       <c r="B187" s="9"/>
       <c r="C187" s="13"/>
@@ -5270,41 +5242,35 @@
       <c r="O187" s="9"/>
       <c r="P187" s="9"/>
     </row>
-    <row r="188" spans="1:16">
-      <c r="A188" s="9"/>
-      <c r="B188" s="9"/>
-      <c r="C188" s="13"/>
-      <c r="D188" s="9"/>
-      <c r="E188" s="9"/>
-      <c r="F188" s="9"/>
-      <c r="G188" s="9"/>
-      <c r="H188" s="9"/>
-      <c r="I188" s="9"/>
-      <c r="J188" s="9"/>
-      <c r="K188" s="9"/>
-      <c r="L188" s="9"/>
-      <c r="M188" s="9"/>
-      <c r="N188" s="9"/>
-      <c r="O188" s="9"/>
-      <c r="P188" s="9"/>
+    <row r="188" ht="14.75" spans="1:16">
+      <c r="A188" s="14"/>
+      <c r="B188" s="14"/>
+      <c r="C188" s="14"/>
+      <c r="D188" s="14"/>
+      <c r="E188" s="14"/>
+      <c r="F188" s="14"/>
+      <c r="G188" s="14"/>
+      <c r="H188" s="14"/>
+      <c r="I188" s="14"/>
+      <c r="J188" s="14"/>
+      <c r="K188" s="14"/>
+      <c r="L188" s="14"/>
+      <c r="M188" s="14"/>
     </row>
     <row r="189" ht="14.75" spans="1:16">
-      <c r="A189" s="9"/>
-      <c r="B189" s="9"/>
-      <c r="C189" s="13"/>
-      <c r="D189" s="9"/>
-      <c r="E189" s="9"/>
-      <c r="F189" s="9"/>
-      <c r="G189" s="9"/>
-      <c r="H189" s="9"/>
-      <c r="I189" s="9"/>
-      <c r="J189" s="9"/>
-      <c r="K189" s="9"/>
-      <c r="L189" s="9"/>
-      <c r="M189" s="9"/>
-      <c r="N189" s="9"/>
-      <c r="O189" s="9"/>
-      <c r="P189" s="9"/>
+      <c r="A189" s="14"/>
+      <c r="B189" s="14"/>
+      <c r="C189" s="14"/>
+      <c r="D189" s="14"/>
+      <c r="E189" s="14"/>
+      <c r="F189" s="14"/>
+      <c r="G189" s="14"/>
+      <c r="H189" s="14"/>
+      <c r="I189" s="14"/>
+      <c r="J189" s="14"/>
+      <c r="K189" s="14"/>
+      <c r="L189" s="14"/>
+      <c r="M189" s="14"/>
     </row>
     <row r="190" ht="14.75" spans="1:16">
       <c r="A190" s="14"/>
@@ -5321,38 +5287,8 @@
       <c r="L190" s="14"/>
       <c r="M190" s="14"/>
     </row>
-    <row r="191" ht="14.75" spans="1:16">
-      <c r="A191" s="14"/>
-      <c r="B191" s="14"/>
-      <c r="C191" s="14"/>
-      <c r="D191" s="14"/>
-      <c r="E191" s="14"/>
-      <c r="F191" s="14"/>
-      <c r="G191" s="14"/>
-      <c r="H191" s="14"/>
-      <c r="I191" s="14"/>
-      <c r="J191" s="14"/>
-      <c r="K191" s="14"/>
-      <c r="L191" s="14"/>
-      <c r="M191" s="14"/>
-    </row>
-    <row r="192" ht="14.75" spans="1:16">
-      <c r="A192" s="14"/>
-      <c r="B192" s="14"/>
-      <c r="C192" s="14"/>
-      <c r="D192" s="14"/>
-      <c r="E192" s="14"/>
-      <c r="F192" s="14"/>
-      <c r="G192" s="14"/>
-      <c r="H192" s="14"/>
-      <c r="I192" s="14"/>
-      <c r="J192" s="14"/>
-      <c r="K192" s="14"/>
-      <c r="L192" s="14"/>
-      <c r="M192" s="14"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P148" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P146" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
